--- a/diseases/d065/2026-2029.xlsx
+++ b/diseases/d065/2026-2029.xlsx
@@ -22410,6 +22410,154 @@
         </is>
       </c>
     </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>monkeypox</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>猴痘</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N136" t="n">
+        <v>7</v>
+      </c>
+      <c r="O136" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.005717658852960364</v>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO136" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP136" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR136" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr"/>
+      <c r="AT136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU136" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV136" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA136" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB136" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC136" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22443,7 +22591,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -22526,7 +22674,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10">
@@ -22536,7 +22684,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -22588,7 +22736,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>860</v>
+        <v>867</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d065/2026-2029.xlsx
+++ b/diseases/d065/2026-2029.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>11</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1454,9 +1451,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1602,9 +1596,6 @@
       <c r="O7" t="n">
         <v>1</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0.001937969923792046</v>
       </c>
@@ -1750,9 +1741,6 @@
       <c r="O8" t="n">
         <v>4</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.07075903303182025</v>
       </c>
@@ -2395,7 +2383,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -4170,9 +4158,6 @@
       <c r="O23" t="n">
         <v>5</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="S23" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4711,9 +4696,6 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
@@ -4859,9 +4841,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -5007,9 +4986,6 @@
       <c r="O28" t="n">
         <v>1</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.01768975825795506</v>
       </c>
@@ -5652,7 +5628,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7279,9 +7255,6 @@
       <c r="O42" t="n">
         <v>4</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="S42" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7820,9 +7793,6 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
@@ -7968,9 +7938,6 @@
       <c r="O46" t="n">
         <v>3</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.005813909771376137</v>
       </c>
@@ -8116,9 +8083,6 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -8761,7 +8725,7 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN50" t="b">
@@ -10240,9 +10204,6 @@
       <c r="O60" t="n">
         <v>58</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.2130230855321478</v>
       </c>
@@ -10388,9 +10349,6 @@
       <c r="O61" t="n">
         <v>2</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="S61" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10929,9 +10887,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -11077,9 +11032,6 @@
       <c r="O65" t="n">
         <v>1</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.001937969923792046</v>
       </c>
@@ -11225,9 +11177,6 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
@@ -11621,9 +11570,6 @@
       <c r="O68" t="n">
         <v>1</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.01891260466471829</v>
       </c>
@@ -11870,7 +11816,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -12017,9 +11963,6 @@
       <c r="O70" t="n">
         <v>2</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.008691384892873792</v>
       </c>
@@ -13349,9 +13292,6 @@
       <c r="O79" t="n">
         <v>49</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.1799677791564697</v>
       </c>
@@ -13497,9 +13437,6 @@
       <c r="O80" t="n">
         <v>2</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="S80" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14038,9 +13975,6 @@
       <c r="O83" t="n">
         <v>3</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0.04065810840590128</v>
       </c>
@@ -14186,9 +14120,6 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
@@ -14334,9 +14265,6 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
@@ -14730,9 +14658,6 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
@@ -14979,7 +14904,7 @@
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN88" t="b">
@@ -15126,9 +15051,6 @@
       <c r="O89" t="n">
         <v>6</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0.02607415467862137</v>
       </c>
@@ -16606,9 +16528,6 @@
       <c r="O99" t="n">
         <v>5</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.001432519066384693</v>
       </c>
@@ -16754,9 +16673,6 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
@@ -17050,9 +16966,6 @@
       <c r="O102" t="n">
         <v>5</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.06776351400983546</v>
       </c>
@@ -17198,9 +17111,6 @@
       <c r="O103" t="n">
         <v>1</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0.001937969923792046</v>
       </c>
@@ -17346,9 +17256,6 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
@@ -17742,9 +17649,6 @@
       <c r="O106" t="n">
         <v>1</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.01891260466471829</v>
       </c>
@@ -17991,7 +17895,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -18138,9 +18042,6 @@
       <c r="O108" t="n">
         <v>4</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.01738276978574758</v>
       </c>
@@ -18286,9 +18187,6 @@
       <c r="O109" t="n">
         <v>2</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0.001633616815131532</v>
       </c>
@@ -18434,9 +18332,6 @@
       <c r="O110" t="n">
         <v>7</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.00200552669293857</v>
       </c>
@@ -18582,9 +18477,6 @@
       <c r="O111" t="n">
         <v>1</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -18730,9 +18622,6 @@
       <c r="O112" t="n">
         <v>4</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.001146015253107754</v>
       </c>
@@ -18878,9 +18767,6 @@
       <c r="O113" t="n">
         <v>2</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0.001633616815131532</v>
       </c>
@@ -19026,9 +18912,6 @@
       <c r="O114" t="n">
         <v>1</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -19174,9 +19057,6 @@
       <c r="O115" t="n">
         <v>2</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.001633616815131532</v>
       </c>
@@ -19322,9 +19202,6 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0</v>
       </c>
@@ -19470,9 +19347,6 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
@@ -19618,9 +19492,6 @@
       <c r="O118" t="n">
         <v>3</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.005813909771376137</v>
       </c>
@@ -19766,9 +19637,6 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
@@ -20162,9 +20030,6 @@
       <c r="O121" t="n">
         <v>7</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0.03041984712505827</v>
       </c>
@@ -20310,9 +20175,6 @@
       <c r="O122" t="n">
         <v>5</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0.004084042037828832</v>
       </c>
@@ -20458,9 +20320,6 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0</v>
       </c>
@@ -20606,9 +20465,6 @@
       <c r="O124" t="n">
         <v>4</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.003267233630263065</v>
       </c>
@@ -20754,9 +20610,6 @@
       <c r="O125" t="n">
         <v>10</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0.002865038132769385</v>
       </c>
@@ -20902,9 +20755,6 @@
       <c r="O126" t="n">
         <v>2</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.001633616815131532</v>
       </c>
@@ -21050,9 +20900,6 @@
       <c r="O127" t="n">
         <v>7</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0.00200552669293857</v>
       </c>
@@ -21198,9 +21045,6 @@
       <c r="O128" t="n">
         <v>3</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0.002450425222697299</v>
       </c>
@@ -21346,9 +21190,6 @@
       <c r="O129" t="n">
         <v>5</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0.001432519066384693</v>
       </c>
@@ -21494,9 +21335,6 @@
       <c r="O130" t="n">
         <v>9</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.007351275668091897</v>
       </c>
@@ -21642,9 +21480,6 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
@@ -21790,9 +21625,6 @@
       <c r="O132" t="n">
         <v>0</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0</v>
       </c>
@@ -21938,9 +21770,6 @@
       <c r="O133" t="n">
         <v>0</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0</v>
       </c>
@@ -22334,9 +22163,6 @@
       <c r="O135" t="n">
         <v>10</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0.002865038132769385</v>
       </c>
@@ -22482,9 +22308,6 @@
       <c r="O136" t="n">
         <v>7</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.005717658852960364</v>
       </c>
@@ -22555,6 +22378,151 @@
       <c r="BC136" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>monkeypox</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>猴痘</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N137" t="n">
+        <v>13</v>
+      </c>
+      <c r="O137" t="n">
+        <v>13</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.003724549572600201</v>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO137" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP137" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR137" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr"/>
+      <c r="AT137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU137" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV137" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA137" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB137" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC137" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -22591,7 +22559,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -22674,7 +22642,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10">
@@ -22684,7 +22652,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11">
@@ -22736,7 +22704,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>867</v>
+        <v>880</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d065/2026-2029.xlsx
+++ b/diseases/d065/2026-2029.xlsx
@@ -13432,10 +13432,10 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -13588,10 +13588,10 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U81" t="inlineStr">
         <is>
@@ -16774,12 +16774,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -16813,84 +16813,92 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>126</v>
+        <v>7</v>
       </c>
       <c r="O101" t="n">
-        <v>126</v>
-      </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
-      <c r="R101" t="n">
-        <v>0.008917739657742821</v>
+        <v>7</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_MPOX_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR101" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS101" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ101" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_MPOX_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC101" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -16917,17 +16925,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -16961,81 +16969,170 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O102" t="n">
-        <v>5</v>
-      </c>
-      <c r="R102" t="n">
-        <v>0.06776351400983546</v>
-      </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_MPOX_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_MPOX_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>Mpox</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD102" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE102" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF102" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG102" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary mpox notifications; confirmed cases only under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM102" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN102" t="b">
+        <v>1</v>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR102" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS102" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ102" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_MPOX_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC102" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -17067,12 +17164,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -17106,13 +17203,16 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>1</v>
+        <v>126</v>
       </c>
       <c r="O103" t="n">
-        <v>1</v>
+        <v>126</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>0.001937969923792046</v>
+        <v>0.008917739657742821</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -17145,42 +17245,42 @@
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -17212,12 +17312,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -17251,95 +17351,81 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O104" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>0.06776351400983546</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U104" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA104" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ104" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS104" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr"/>
       <c r="AT104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -17366,17 +17452,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -17410,170 +17496,81 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O105" t="n">
-        <v>0</v>
-      </c>
-      <c r="U105" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V105" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W105" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X105" t="inlineStr">
-        <is>
-          <t>M-kopper</t>
-        </is>
-      </c>
-      <c r="Y105" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA105" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD105" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE105" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF105" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG105" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH105" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI105" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ105" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK105" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN105" t="b">
         <v>1</v>
       </c>
+      <c r="R105" t="n">
+        <v>0.001937969923792046</v>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ105" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS105" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr"/>
       <c r="AT105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC105" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -17605,12 +17602,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -17644,13 +17641,13 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>0.01891260466471829</v>
+        <v>0</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -17659,7 +17656,7 @@
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>SER_NZ_MPOX_MONTHLY</t>
+          <t>SER_NO_FHI_714_MONTHLY</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -17684,7 +17681,7 @@
       </c>
       <c r="AS106" t="inlineStr">
         <is>
-          <t>SER_NZ_MPOX_MONTHLY</t>
+          <t>SER_NO_FHI_714_MONTHLY</t>
         </is>
       </c>
       <c r="AT106" t="n">
@@ -17697,42 +17694,42 @@
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -17764,12 +17761,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -17803,29 +17800,29 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>SER_NZ_MPOX_MONTHLY</t>
+          <t>SER_NO_FHI_714_MONTHLY</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>SER_NZ_MPOX_MONTHLY</t>
+          <t>SER_NO_FHI_714_MONTHLY</t>
         </is>
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>SRC_NZ_PHS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>Mpox</t>
+          <t>M-kopper</t>
         </is>
       </c>
       <c r="Y107" t="inlineStr">
@@ -17835,7 +17832,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -17850,7 +17847,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>country:NZ:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD107" t="inlineStr">
@@ -17885,17 +17882,17 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>NZ_PHS_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science monthly mpox notifications.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -17918,7 +17915,7 @@
       </c>
       <c r="AS107" t="inlineStr">
         <is>
-          <t>SER_NZ_MPOX_MONTHLY</t>
+          <t>SER_NO_FHI_714_MONTHLY</t>
         </is>
       </c>
       <c r="AT107" t="n">
@@ -17931,42 +17928,42 @@
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -17998,12 +17995,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -18037,81 +18034,95 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O108" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R108" t="n">
-        <v>0.01738276978574758</v>
+        <v>0.01891260466471829</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>SER_NZ_MPOX_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR108" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS108" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ108" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr">
+        <is>
+          <t>SER_NZ_MPOX_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC108" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -18138,17 +18149,17 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -18173,7 +18184,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -18182,56 +18193,145 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O109" t="n">
-        <v>2</v>
-      </c>
-      <c r="R109" t="n">
-        <v>0.001633616815131532</v>
-      </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>SER_NZ_MPOX_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>SER_NZ_MPOX_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>Mpox</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD109" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE109" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF109" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG109" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly mpox notifications.</t>
+        </is>
+      </c>
+      <c r="AM109" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN109" t="b">
+        <v>1</v>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR109" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS109" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ109" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr">
+        <is>
+          <t>SER_NZ_MPOX_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -18241,17 +18341,17 @@
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC109" t="inlineStr">
@@ -18288,12 +18388,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -18318,7 +18418,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -18327,13 +18427,13 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O110" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R110" t="n">
-        <v>0.00200552669293857</v>
+        <v>0.01738276978574758</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -18366,42 +18466,42 @@
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC110" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -18463,7 +18563,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -18472,13 +18572,13 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R111" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -18608,7 +18708,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -18617,13 +18717,13 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O112" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R112" t="n">
-        <v>0.001146015253107754</v>
+        <v>0.00200552669293857</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -18753,7 +18853,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -18762,13 +18862,13 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R113" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -18898,7 +18998,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -18907,13 +19007,13 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O114" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R114" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0.001146015253107754</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -19043,7 +19143,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -19188,7 +19288,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -19197,13 +19297,13 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -19303,12 +19403,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -19333,22 +19433,22 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -19381,42 +19481,42 @@
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19448,12 +19548,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -19478,22 +19578,22 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N118" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>0.005813909771376137</v>
+        <v>0</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
@@ -19526,42 +19626,42 @@
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -19593,12 +19693,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -19645,82 +19745,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U119" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA119" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ119" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS119" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr"/>
       <c r="AT119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -19747,17 +19833,17 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -19791,170 +19877,81 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O120" t="n">
-        <v>0</v>
-      </c>
-      <c r="U120" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V120" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W120" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X120" t="inlineStr">
-        <is>
-          <t>M-kopper</t>
-        </is>
-      </c>
-      <c r="Y120" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA120" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD120" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE120" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF120" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG120" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI120" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ120" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK120" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN120" t="b">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.005813909771376137</v>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ120" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS120" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr"/>
       <c r="AT120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -19986,12 +19983,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -20025,81 +20022,95 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>0.03041984712505827</v>
+        <v>0</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_714_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR121" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS121" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ121" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_714_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -20126,17 +20137,17 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -20161,7 +20172,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -20170,81 +20181,170 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
-        <v>5</v>
-      </c>
-      <c r="R122" t="n">
-        <v>0.004084042037828832</v>
-      </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_714_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_714_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>M-kopper</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD122" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF122" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG122" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM122" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN122" t="b">
+        <v>1</v>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR122" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS122" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ122" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_714_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -20276,12 +20376,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -20306,7 +20406,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -20315,13 +20415,13 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O123" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>0.03041984712505827</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
@@ -20354,42 +20454,42 @@
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -20451,7 +20551,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -20460,13 +20560,13 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O124" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R124" t="n">
-        <v>0.003267233630263065</v>
+        <v>0.004084042037828832</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -20596,7 +20696,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -20605,13 +20705,13 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>0.002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S125" t="inlineStr">
         <is>
@@ -20741,7 +20841,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -20750,13 +20850,13 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O126" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R126" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.003267233630263065</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
@@ -20886,7 +20986,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -20895,13 +20995,13 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O127" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R127" t="n">
-        <v>0.00200552669293857</v>
+        <v>0.002865038132769385</v>
       </c>
       <c r="S127" t="inlineStr">
         <is>
@@ -21031,7 +21131,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -21040,13 +21140,13 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O128" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R128" t="n">
-        <v>0.002450425222697299</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
@@ -21176,7 +21276,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -21185,13 +21285,13 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O129" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R129" t="n">
-        <v>0.001432519066384693</v>
+        <v>0.00200552669293857</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
@@ -21321,7 +21421,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -21330,13 +21430,13 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O130" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="R130" t="n">
-        <v>0.007351275668091897</v>
+        <v>0.002450425222697299</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
@@ -21436,12 +21536,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -21466,22 +21566,22 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O131" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R131" t="n">
-        <v>0</v>
+        <v>0.001432519066384693</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
@@ -21514,42 +21614,42 @@
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -21581,12 +21681,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -21611,22 +21711,22 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O132" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R132" t="n">
-        <v>0</v>
+        <v>0.007351275668091897</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -21659,42 +21759,42 @@
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21726,12 +21826,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -21765,95 +21865,81 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O133" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R133" t="n">
-        <v>0</v>
+        <v>0.02570968273663853</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U133" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA133" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO133" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ133" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS133" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR133" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS133" t="inlineStr"/>
       <c r="AT133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -21880,17 +21966,17 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -21929,165 +22015,76 @@
       <c r="O134" t="n">
         <v>0</v>
       </c>
-      <c r="U134" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V134" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W134" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X134" t="inlineStr">
-        <is>
-          <t>M-kopper</t>
-        </is>
-      </c>
-      <c r="Y134" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA134" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD134" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE134" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF134" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG134" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH134" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI134" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ134" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK134" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM134" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN134" t="b">
-        <v>1</v>
+      <c r="R134" t="n">
+        <v>0</v>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO134" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ134" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS134" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR134" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS134" t="inlineStr"/>
       <c r="AT134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -22119,12 +22116,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -22158,81 +22155,95 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>0.002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_714_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR135" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS135" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ135" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_714_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -22259,17 +22270,17 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -22294,7 +22305,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -22303,81 +22314,170 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
-        <v>7</v>
-      </c>
-      <c r="R136" t="n">
-        <v>0.005717658852960364</v>
-      </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_714_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_714_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X136" t="inlineStr">
+        <is>
+          <t>M-kopper</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD136" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE136" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF136" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG136" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH136" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ136" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK136" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM136" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN136" t="b">
+        <v>1</v>
       </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR136" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS136" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ136" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_714_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -22439,7 +22539,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -22448,13 +22548,13 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O137" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="R137" t="n">
-        <v>0.003724549572600201</v>
+        <v>0.002865038132769385</v>
       </c>
       <c r="S137" t="inlineStr">
         <is>
@@ -22521,6 +22621,296 @@
         </is>
       </c>
       <c r="BC137" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>monkeypox</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>猴痘</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N138" t="n">
+        <v>7</v>
+      </c>
+      <c r="O138" t="n">
+        <v>7</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.005717658852960364</v>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO138" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP138" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR138" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS138" t="inlineStr"/>
+      <c r="AT138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU138" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV138" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA138" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB138" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC138" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>monkeypox</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>猴痘</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N139" t="n">
+        <v>13</v>
+      </c>
+      <c r="O139" t="n">
+        <v>13</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.003724549572600201</v>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO139" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP139" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR139" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS139" t="inlineStr"/>
+      <c r="AT139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU139" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV139" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA139" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB139" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC139" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -22642,7 +23032,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10">
@@ -22652,7 +23042,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11">
@@ -22672,7 +23062,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -22704,7 +23094,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>880</v>
+        <v>895</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d065/2026-2029.xlsx
+++ b/diseases/d065/2026-2029.xlsx
@@ -21865,13 +21865,13 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O133" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R133" t="n">
-        <v>0.02570968273663853</v>
+        <v>0.03305530637567811</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -22913,6 +22913,151 @@
       <c r="BC139" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>monkeypox</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>猴痘</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N140" t="n">
+        <v>6</v>
+      </c>
+      <c r="O140" t="n">
+        <v>6</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.004900850445394598</v>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO140" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP140" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR140" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr"/>
+      <c r="AT140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU140" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV140" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA140" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB140" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC140" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22949,7 +23094,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -23032,7 +23177,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10">
@@ -23042,7 +23187,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11">
@@ -23094,7 +23239,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>895</v>
+        <v>903</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d065/2026-2029.xlsx
+++ b/diseases/d065/2026-2029.xlsx
@@ -19838,12 +19838,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -19877,13 +19877,16 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>3</v>
+        <v>83</v>
       </c>
       <c r="O120" t="n">
-        <v>3</v>
+        <v>83</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>0.005813909771376137</v>
+        <v>0.00587438406025916</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -19916,42 +19919,42 @@
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -19983,12 +19986,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -20022,95 +20025,81 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O121" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>0.005813909771376137</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U121" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA121" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ121" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS121" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr"/>
       <c r="AT121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -20137,7 +20126,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -20186,98 +20175,23 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U122" t="inlineStr">
         <is>
           <t>SER_NO_FHI_714_MONTHLY</t>
         </is>
       </c>
-      <c r="V122" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W122" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X122" t="inlineStr">
-        <is>
-          <t>M-kopper</t>
-        </is>
-      </c>
-      <c r="Y122" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD122" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE122" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF122" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG122" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH122" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI122" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ122" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK122" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN122" t="b">
-        <v>1</v>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
@@ -20371,17 +20285,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -20415,81 +20329,170 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
-        <v>7</v>
-      </c>
-      <c r="R123" t="n">
-        <v>0.03041984712505827</v>
-      </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_714_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_714_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>M-kopper</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD123" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM123" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN123" t="b">
+        <v>1</v>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR123" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS123" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_714_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -20521,12 +20524,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -20551,7 +20554,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -20560,13 +20563,13 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O124" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R124" t="n">
-        <v>0.004084042037828832</v>
+        <v>0.03041984712505827</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -20599,42 +20602,42 @@
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -20666,12 +20669,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -20705,13 +20708,13 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O125" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>0.004084042037828832</v>
       </c>
       <c r="S125" t="inlineStr">
         <is>
@@ -20744,42 +20747,42 @@
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -20811,12 +20814,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -20841,7 +20844,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -20850,13 +20853,13 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>0.003267233630263065</v>
+        <v>0</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
@@ -20889,42 +20892,42 @@
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -20956,12 +20959,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -20995,13 +20998,13 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O127" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="R127" t="n">
-        <v>0.002865038132769385</v>
+        <v>0.003267233630263065</v>
       </c>
       <c r="S127" t="inlineStr">
         <is>
@@ -21034,42 +21037,42 @@
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21101,12 +21104,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -21131,7 +21134,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -21140,13 +21143,13 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="O128" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="R128" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.002865038132769385</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
@@ -21179,42 +21182,42 @@
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB128" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC128" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -21246,12 +21249,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -21285,13 +21288,13 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O129" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R129" t="n">
-        <v>0.00200552669293857</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
@@ -21324,42 +21327,42 @@
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21391,12 +21394,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -21421,7 +21424,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -21430,13 +21433,13 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O130" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R130" t="n">
-        <v>0.002450425222697299</v>
+        <v>0.00200552669293857</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
@@ -21469,42 +21472,42 @@
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -21536,12 +21539,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -21575,13 +21578,13 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O131" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R131" t="n">
-        <v>0.001432519066384693</v>
+        <v>0.002450425222697299</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
@@ -21614,42 +21617,42 @@
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21681,12 +21684,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -21711,7 +21714,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -21720,13 +21723,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="O132" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="R132" t="n">
-        <v>0.007351275668091897</v>
+        <v>0.001432519066384693</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -21759,42 +21762,42 @@
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -21826,12 +21829,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -21856,12 +21859,12 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N133" t="n">
@@ -21871,7 +21874,7 @@
         <v>9</v>
       </c>
       <c r="R133" t="n">
-        <v>0.03305530637567811</v>
+        <v>0.007351275668091897</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -21904,42 +21907,42 @@
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21971,12 +21974,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -22010,13 +22013,13 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O134" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R134" t="n">
-        <v>0</v>
+        <v>0.03305530637567811</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -22049,42 +22052,42 @@
       </c>
       <c r="AV134" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -22116,12 +22119,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -22168,82 +22171,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U135" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA135" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO135" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ135" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS135" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR135" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr"/>
       <c r="AT135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -22270,7 +22259,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -22319,98 +22308,23 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
+      <c r="R136" t="n">
+        <v>0</v>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U136" t="inlineStr">
         <is>
           <t>SER_NO_FHI_714_MONTHLY</t>
         </is>
       </c>
-      <c r="V136" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W136" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X136" t="inlineStr">
-        <is>
-          <t>M-kopper</t>
-        </is>
-      </c>
-      <c r="Y136" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD136" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE136" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF136" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG136" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH136" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI136" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ136" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK136" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM136" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN136" t="b">
-        <v>1</v>
       </c>
       <c r="AO136" t="inlineStr">
         <is>
@@ -22504,17 +22418,17 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -22548,81 +22462,170 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
-        <v>10</v>
-      </c>
-      <c r="R137" t="n">
-        <v>0.002865038132769385</v>
-      </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_714_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_714_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t>M-kopper</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD137" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE137" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF137" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG137" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK137" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM137" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN137" t="b">
+        <v>1</v>
       </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR137" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS137" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ137" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_714_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -22654,12 +22657,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -22684,7 +22687,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -22693,13 +22696,13 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O138" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R138" t="n">
-        <v>0.005717658852960364</v>
+        <v>0.002865038132769385</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -22732,42 +22735,42 @@
       </c>
       <c r="AV138" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB138" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC138" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -22799,12 +22802,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -22829,7 +22832,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -22838,13 +22841,13 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="O139" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="R139" t="n">
-        <v>0.003724549572600201</v>
+        <v>0.005717658852960364</v>
       </c>
       <c r="S139" t="inlineStr">
         <is>
@@ -22877,42 +22880,42 @@
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22944,12 +22947,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -22974,7 +22977,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -22983,13 +22986,13 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="O140" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="R140" t="n">
-        <v>0.004900850445394598</v>
+        <v>0.003724549572600201</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -23022,40 +23025,185 @@
       </c>
       <c r="AV140" t="inlineStr">
         <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA140" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB140" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC140" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>monkeypox</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>猴痘</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N141" t="n">
+        <v>6</v>
+      </c>
+      <c r="O141" t="n">
+        <v>6</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.004900850445394598</v>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO141" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP141" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR141" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr"/>
+      <c r="AT141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU141" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV141" t="inlineStr">
+        <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW140" t="inlineStr">
+      <c r="AW141" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX140" t="inlineStr">
+      <c r="AX141" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY140" t="inlineStr">
+      <c r="AY141" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ140" t="inlineStr">
+      <c r="AZ141" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA140" t="inlineStr">
+      <c r="BA141" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB140" t="inlineStr">
+      <c r="BB141" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC140" t="inlineStr">
+      <c r="BC141" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -23177,7 +23325,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10">
@@ -23187,7 +23335,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -23239,7 +23387,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>903</v>
+        <v>986</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d065/2026-2029.xlsx
+++ b/diseases/d065/2026-2029.xlsx
@@ -22013,13 +22013,13 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="O134" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="R134" t="n">
-        <v>0.03305530637567811</v>
+        <v>0.04407374183423748</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -23206,6 +23206,151 @@
       <c r="BC141" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>monkeypox</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>猴痘</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N142" t="n">
+        <v>7</v>
+      </c>
+      <c r="O142" t="n">
+        <v>7</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.00200552669293857</v>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO142" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP142" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr"/>
+      <c r="AT142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU142" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV142" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA142" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB142" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC142" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -23242,7 +23387,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -23325,7 +23470,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10">
@@ -23335,7 +23480,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11">
@@ -23387,7 +23532,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>986</v>
+        <v>996</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d065/2026-2029.xlsx
+++ b/diseases/d065/2026-2029.xlsx
@@ -22013,13 +22013,13 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O134" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R134" t="n">
-        <v>0.04407374183423748</v>
+        <v>0.04774655365375727</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -23532,7 +23532,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>996</v>
+        <v>997</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d065/2026-2029.xlsx
+++ b/diseases/d065/2026-2029.xlsx
@@ -18034,13 +18034,13 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>0.01891260466471829</v>
+        <v>0</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -18193,10 +18193,10 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U109" t="inlineStr">
         <is>
@@ -20524,12 +20524,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -20563,81 +20563,95 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O124" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R124" t="n">
-        <v>0.03041984712505827</v>
+        <v>0.01891260466471829</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>SER_NZ_MPOX_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR124" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS124" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ124" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>SER_NZ_MPOX_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -20664,17 +20678,17 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -20699,7 +20713,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -20708,56 +20722,145 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O125" t="n">
-        <v>5</v>
-      </c>
-      <c r="R125" t="n">
-        <v>0.004084042037828832</v>
-      </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>SER_NZ_MPOX_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>SER_NZ_MPOX_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>Mpox</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD125" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly mpox notifications.</t>
+        </is>
+      </c>
+      <c r="AM125" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN125" t="b">
+        <v>1</v>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR125" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS125" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>SER_NZ_MPOX_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -20767,17 +20870,17 @@
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
@@ -20814,12 +20917,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -20844,7 +20947,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -20853,13 +20956,13 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O126" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>0.03041984712505827</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
@@ -20892,42 +20995,42 @@
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -20989,7 +21092,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -20998,13 +21101,13 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O127" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R127" t="n">
-        <v>0.003267233630263065</v>
+        <v>0.004084042037828832</v>
       </c>
       <c r="S127" t="inlineStr">
         <is>
@@ -21134,7 +21237,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -21143,13 +21246,13 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>0.002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
@@ -21279,7 +21382,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -21288,13 +21391,13 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O129" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R129" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.003267233630263065</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
@@ -21424,7 +21527,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -21433,13 +21536,13 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O130" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R130" t="n">
-        <v>0.00200552669293857</v>
+        <v>0.002865038132769385</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
@@ -21569,7 +21672,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -21578,13 +21681,13 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R131" t="n">
-        <v>0.002450425222697299</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
@@ -21714,7 +21817,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -21723,13 +21826,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O132" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R132" t="n">
-        <v>0.001432519066384693</v>
+        <v>0.00200552669293857</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -21859,7 +21962,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -21868,13 +21971,13 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O133" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="R133" t="n">
-        <v>0.007351275668091897</v>
+        <v>0.002450425222697299</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -21974,12 +22077,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -22004,22 +22107,22 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N134" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="O134" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="R134" t="n">
-        <v>0.04774655365375727</v>
+        <v>0.001432519066384693</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -22052,42 +22155,42 @@
       </c>
       <c r="AV134" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -22119,12 +22222,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -22149,22 +22252,22 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O135" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R135" t="n">
-        <v>0</v>
+        <v>0.007351275668091897</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
@@ -22197,42 +22300,42 @@
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22264,12 +22367,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -22303,95 +22406,81 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O136" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="R136" t="n">
-        <v>0</v>
+        <v>0.06978342457087601</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U136" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA136" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ136" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS136" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR136" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr"/>
       <c r="AT136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -22418,17 +22507,17 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -22467,165 +22556,76 @@
       <c r="O137" t="n">
         <v>0</v>
       </c>
-      <c r="U137" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V137" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W137" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X137" t="inlineStr">
-        <is>
-          <t>M-kopper</t>
-        </is>
-      </c>
-      <c r="Y137" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z137" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA137" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB137" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD137" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE137" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF137" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG137" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH137" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI137" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ137" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK137" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM137" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN137" t="b">
-        <v>1</v>
+      <c r="R137" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ137" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS137" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR137" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr"/>
       <c r="AT137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -22657,12 +22657,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -22696,81 +22696,95 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O138" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>0.002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_714_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR138" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS138" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ138" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS138" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_714_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB138" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC138" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -22797,17 +22811,17 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -22832,7 +22846,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -22841,81 +22855,170 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O139" t="n">
-        <v>7</v>
-      </c>
-      <c r="R139" t="n">
-        <v>0.005717658852960364</v>
-      </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_714_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_714_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>M-kopper</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD139" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF139" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG139" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK139" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM139" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN139" t="b">
+        <v>1</v>
       </c>
       <c r="AO139" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR139" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS139" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ139" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS139" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_714_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -22977,7 +23080,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -22986,13 +23089,13 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O140" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="R140" t="n">
-        <v>0.003724549572600201</v>
+        <v>0.002865038132769385</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -23122,7 +23225,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -23131,13 +23234,13 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O141" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R141" t="n">
-        <v>0.004900850445394598</v>
+        <v>0.005717658852960364</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -23267,7 +23370,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -23276,13 +23379,13 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O142" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="R142" t="n">
-        <v>0.00200552669293857</v>
+        <v>0.003724549572600201</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -23351,6 +23454,441 @@
       <c r="BC142" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>monkeypox</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>猴痘</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N143" t="n">
+        <v>6</v>
+      </c>
+      <c r="O143" t="n">
+        <v>6</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.004900850445394598</v>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP143" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR143" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr"/>
+      <c r="AT143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU143" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV143" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA143" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB143" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC143" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>monkeypox</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>猴痘</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N144" t="n">
+        <v>7</v>
+      </c>
+      <c r="O144" t="n">
+        <v>7</v>
+      </c>
+      <c r="R144" t="n">
+        <v>0.00200552669293857</v>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP144" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR144" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr"/>
+      <c r="AT144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU144" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV144" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA144" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB144" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC144" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>monkeypox</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>猴痘</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N145" t="n">
+        <v>4</v>
+      </c>
+      <c r="O145" t="n">
+        <v>4</v>
+      </c>
+      <c r="R145" t="n">
+        <v>0.003267233630263065</v>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP145" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR145" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr"/>
+      <c r="AT145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU145" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV145" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA145" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB145" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC145" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23387,7 +23925,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -23470,7 +24008,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10">
@@ -23480,7 +24018,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11">
@@ -23500,7 +24038,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -23532,7 +24070,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>997</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d065/2026-2029.xlsx
+++ b/diseases/d065/2026-2029.xlsx
@@ -22406,13 +22406,13 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O136" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R136" t="n">
-        <v>0.06978342457087601</v>
+        <v>0.07345623639039579</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -24070,7 +24070,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1007</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d065/2026-2029.xlsx
+++ b/diseases/d065/2026-2029.xlsx
@@ -30230,12 +30230,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -30269,13 +30269,13 @@
         </is>
       </c>
       <c r="N173" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O173" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R173" t="n">
-        <v>0.005813909771376137</v>
+        <v>0.01355270280196709</v>
       </c>
       <c r="S173" t="inlineStr">
         <is>
@@ -30308,42 +30308,42 @@
       </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA173" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB173" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC173" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -30375,12 +30375,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -30414,95 +30414,81 @@
         </is>
       </c>
       <c r="N174" t="n">
+        <v>3</v>
+      </c>
+      <c r="O174" t="n">
+        <v>3</v>
+      </c>
+      <c r="R174" t="n">
+        <v>0.005813909771376137</v>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO174" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP174" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR174" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS174" t="inlineStr"/>
+      <c r="AT174" t="n">
         <v>0</v>
       </c>
-      <c r="O174" t="n">
-        <v>0</v>
-      </c>
-      <c r="R174" t="n">
-        <v>0</v>
-      </c>
-      <c r="S174" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U174" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA174" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO174" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP174" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ174" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS174" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT174" t="n">
-        <v>1</v>
-      </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA174" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB174" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC174" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -30529,7 +30515,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -30578,98 +30564,23 @@
       <c r="O175" t="n">
         <v>0</v>
       </c>
+      <c r="R175" t="n">
+        <v>0</v>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U175" t="inlineStr">
         <is>
           <t>SER_NO_FHI_714_MONTHLY</t>
         </is>
       </c>
-      <c r="V175" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W175" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X175" t="inlineStr">
-        <is>
-          <t>M-kopper</t>
-        </is>
-      </c>
-      <c r="Y175" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z175" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA175" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB175" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD175" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE175" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF175" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG175" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH175" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI175" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ175" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK175" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM175" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN175" t="b">
-        <v>1</v>
       </c>
       <c r="AO175" t="inlineStr">
         <is>
@@ -30763,17 +30674,17 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -30807,29 +30718,104 @@
         </is>
       </c>
       <c r="N176" t="n">
+        <v>0</v>
+      </c>
+      <c r="O176" t="n">
+        <v>0</v>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_714_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_714_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X176" t="inlineStr">
+        <is>
+          <t>M-kopper</t>
+        </is>
+      </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD176" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE176" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF176" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG176" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH176" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI176" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ176" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK176" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM176" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN176" t="b">
         <v>1</v>
       </c>
-      <c r="O176" t="n">
-        <v>1</v>
-      </c>
-      <c r="R176" t="n">
-        <v>0.01891260466471829</v>
-      </c>
-      <c r="S176" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U176" t="inlineStr">
-        <is>
-          <t>SER_NZ_MPOX_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA176" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO176" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -30847,7 +30833,7 @@
       </c>
       <c r="AS176" t="inlineStr">
         <is>
-          <t>SER_NZ_MPOX_MONTHLY</t>
+          <t>SER_NO_FHI_714_MONTHLY</t>
         </is>
       </c>
       <c r="AT176" t="n">
@@ -30860,42 +30846,42 @@
       </c>
       <c r="AV176" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA176" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB176" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC176" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -30922,7 +30908,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -30971,98 +30957,23 @@
       <c r="O177" t="n">
         <v>1</v>
       </c>
+      <c r="R177" t="n">
+        <v>0.01891260466471829</v>
+      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U177" t="inlineStr">
         <is>
           <t>SER_NZ_MPOX_MONTHLY</t>
         </is>
       </c>
-      <c r="V177" t="inlineStr">
-        <is>
-          <t>SER_NZ_MPOX_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W177" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X177" t="inlineStr">
-        <is>
-          <t>Mpox</t>
-        </is>
-      </c>
-      <c r="Y177" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z177" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA177" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB177" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD177" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE177" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF177" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG177" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH177" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI177" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ177" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK177" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly mpox notifications.</t>
-        </is>
-      </c>
-      <c r="AM177" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN177" t="b">
-        <v>1</v>
       </c>
       <c r="AO177" t="inlineStr">
         <is>
@@ -31156,17 +31067,17 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -31200,81 +31111,170 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O178" t="n">
-        <v>7</v>
-      </c>
-      <c r="R178" t="n">
-        <v>0.03041984712505827</v>
-      </c>
-      <c r="S178" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>SER_NZ_MPOX_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>SER_NZ_MPOX_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W178" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X178" t="inlineStr">
+        <is>
+          <t>Mpox</t>
+        </is>
+      </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB178" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD178" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE178" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF178" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG178" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH178" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI178" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ178" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK178" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly mpox notifications.</t>
+        </is>
+      </c>
+      <c r="AM178" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN178" t="b">
+        <v>1</v>
       </c>
       <c r="AO178" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP178" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR178" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS178" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ178" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS178" t="inlineStr">
+        <is>
+          <t>SER_NZ_MPOX_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU178" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV178" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA178" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB178" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC178" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -31306,12 +31306,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -31336,7 +31336,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -31345,13 +31345,13 @@
         </is>
       </c>
       <c r="N179" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O179" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R179" t="n">
-        <v>0.004084042037828832</v>
+        <v>0.03041984712505827</v>
       </c>
       <c r="S179" t="inlineStr">
         <is>
@@ -31384,42 +31384,42 @@
       </c>
       <c r="AV179" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA179" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB179" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC179" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -31451,12 +31451,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -31490,13 +31490,13 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O180" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R180" t="n">
-        <v>0</v>
+        <v>0.004084042037828832</v>
       </c>
       <c r="S180" t="inlineStr">
         <is>
@@ -31529,42 +31529,42 @@
       </c>
       <c r="AV180" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA180" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB180" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC180" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -31596,12 +31596,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -31626,7 +31626,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -31635,93 +31635,81 @@
         </is>
       </c>
       <c r="N181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O181" t="n">
-        <v>1</v>
-      </c>
-      <c r="P181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R181" t="n">
-        <v>0.01693265755097047</v>
+        <v>0</v>
       </c>
       <c r="S181" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA181" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO181" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ181" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS181" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR181" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS181" t="inlineStr"/>
       <c r="AT181" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV181" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA181" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB181" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC181" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -31748,7 +31736,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -31800,98 +31788,18 @@
       <c r="P182" t="n">
         <v>1</v>
       </c>
-      <c r="U182" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX</t>
-        </is>
-      </c>
-      <c r="V182" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX</t>
-        </is>
-      </c>
-      <c r="W182" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X182" t="inlineStr">
-        <is>
-          <t>Mpox</t>
-        </is>
-      </c>
-      <c r="Y182" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z182" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R182" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB182" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC182" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD182" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE182" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF182" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG182" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH182" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI182" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ182" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK182" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM182" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN182" t="b">
-        <v>1</v>
       </c>
       <c r="AO182" t="inlineStr">
         <is>
@@ -31985,17 +31893,17 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -32020,7 +31928,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -32029,81 +31937,173 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O183" t="n">
-        <v>4</v>
-      </c>
-      <c r="R183" t="n">
-        <v>0.003267233630263065</v>
-      </c>
-      <c r="S183" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P183" t="n">
+        <v>1</v>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X183" t="inlineStr">
+        <is>
+          <t>Mpox</t>
+        </is>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z183" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB183" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD183" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE183" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF183" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG183" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH183" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI183" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ183" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK183" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM183" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN183" t="b">
+        <v>1</v>
       </c>
       <c r="AO183" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP183" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR183" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS183" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ183" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS183" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
+        </is>
+      </c>
       <c r="AT183" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU183" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV183" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA183" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB183" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC183" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -32135,12 +32135,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -32174,13 +32174,13 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O184" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="R184" t="n">
-        <v>0.002865038132769385</v>
+        <v>0.003267233630263065</v>
       </c>
       <c r="S184" t="inlineStr">
         <is>
@@ -32213,42 +32213,42 @@
       </c>
       <c r="AV184" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA184" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB184" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC184" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -32280,12 +32280,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -32310,7 +32310,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -32319,93 +32319,81 @@
         </is>
       </c>
       <c r="N185" t="n">
+        <v>10</v>
+      </c>
+      <c r="O185" t="n">
+        <v>10</v>
+      </c>
+      <c r="R185" t="n">
+        <v>0.002865038132769385</v>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO185" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP185" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR185" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS185" t="inlineStr"/>
+      <c r="AT185" t="n">
         <v>0</v>
       </c>
-      <c r="O185" t="n">
-        <v>0</v>
-      </c>
-      <c r="P185" t="n">
-        <v>0</v>
-      </c>
-      <c r="R185" t="n">
-        <v>0</v>
-      </c>
-      <c r="S185" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA185" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO185" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP185" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ185" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS185" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
-        </is>
-      </c>
-      <c r="AT185" t="n">
-        <v>2</v>
-      </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV185" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA185" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB185" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC185" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -32432,7 +32420,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -32484,98 +32472,18 @@
       <c r="P186" t="n">
         <v>0</v>
       </c>
-      <c r="U186" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX</t>
-        </is>
-      </c>
-      <c r="V186" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX</t>
-        </is>
-      </c>
-      <c r="W186" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X186" t="inlineStr">
-        <is>
-          <t>Mpox</t>
-        </is>
-      </c>
-      <c r="Y186" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z186" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R186" t="n">
+        <v>0</v>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB186" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC186" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD186" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE186" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF186" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG186" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH186" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI186" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ186" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK186" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM186" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN186" t="b">
-        <v>1</v>
       </c>
       <c r="AO186" t="inlineStr">
         <is>
@@ -32669,17 +32577,17 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -32704,7 +32612,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -32713,81 +32621,173 @@
         </is>
       </c>
       <c r="N187" t="n">
+        <v>0</v>
+      </c>
+      <c r="O187" t="n">
+        <v>0</v>
+      </c>
+      <c r="P187" t="n">
+        <v>0</v>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X187" t="inlineStr">
+        <is>
+          <t>Mpox</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD187" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE187" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF187" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG187" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH187" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI187" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ187" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK187" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM187" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN187" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO187" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP187" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ187" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS187" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
+        </is>
+      </c>
+      <c r="AT187" t="n">
         <v>2</v>
       </c>
-      <c r="O187" t="n">
-        <v>2</v>
-      </c>
-      <c r="R187" t="n">
-        <v>0.001633616815131532</v>
-      </c>
-      <c r="S187" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO187" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP187" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR187" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS187" t="inlineStr"/>
-      <c r="AT187" t="n">
-        <v>0</v>
-      </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA187" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB187" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC187" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -32819,12 +32819,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -32858,13 +32858,13 @@
         </is>
       </c>
       <c r="N188" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O188" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R188" t="n">
-        <v>0.00200552669293857</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S188" t="inlineStr">
         <is>
@@ -32897,42 +32897,42 @@
       </c>
       <c r="AV188" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA188" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB188" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC188" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -32964,12 +32964,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -32994,7 +32994,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -33003,93 +33003,81 @@
         </is>
       </c>
       <c r="N189" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O189" t="n">
-        <v>2</v>
-      </c>
-      <c r="P189" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R189" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.00200552669293857</v>
       </c>
       <c r="S189" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA189" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO189" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP189" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ189" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS189" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR189" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS189" t="inlineStr"/>
       <c r="AT189" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU189" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV189" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA189" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB189" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC189" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -33116,7 +33104,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -33168,98 +33156,18 @@
       <c r="P190" t="n">
         <v>2</v>
       </c>
-      <c r="U190" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX</t>
-        </is>
-      </c>
-      <c r="V190" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX</t>
-        </is>
-      </c>
-      <c r="W190" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X190" t="inlineStr">
-        <is>
-          <t>Mpox</t>
-        </is>
-      </c>
-      <c r="Y190" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z190" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R190" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB190" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD190" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE190" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF190" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG190" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH190" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI190" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ190" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK190" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM190" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN190" t="b">
-        <v>1</v>
       </c>
       <c r="AO190" t="inlineStr">
         <is>
@@ -33353,17 +33261,17 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -33388,7 +33296,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -33397,81 +33305,173 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O191" t="n">
-        <v>3</v>
-      </c>
-      <c r="R191" t="n">
-        <v>0.002450425222697299</v>
-      </c>
-      <c r="S191" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P191" t="n">
+        <v>2</v>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X191" t="inlineStr">
+        <is>
+          <t>Mpox</t>
+        </is>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB191" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD191" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE191" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF191" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG191" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH191" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI191" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ191" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK191" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM191" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN191" t="b">
+        <v>1</v>
       </c>
       <c r="AO191" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR191" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS191" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ191" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS191" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
+        </is>
+      </c>
       <c r="AT191" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV191" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA191" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB191" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC191" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -33503,12 +33503,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -33542,13 +33542,13 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O192" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R192" t="n">
-        <v>0.001432519066384693</v>
+        <v>0.002450425222697299</v>
       </c>
       <c r="S192" t="inlineStr">
         <is>
@@ -33581,42 +33581,42 @@
       </c>
       <c r="AV192" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA192" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB192" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC192" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -33648,12 +33648,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -33678,7 +33678,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -33687,13 +33687,13 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="O193" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="R193" t="n">
-        <v>0.007351275668091897</v>
+        <v>0.001432519066384693</v>
       </c>
       <c r="S193" t="inlineStr">
         <is>
@@ -33726,42 +33726,42 @@
       </c>
       <c r="AV193" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA193" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB193" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC193" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -33793,12 +33793,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -33832,93 +33832,81 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O194" t="n">
-        <v>1</v>
-      </c>
-      <c r="P194" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="R194" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.007351275668091897</v>
       </c>
       <c r="S194" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA194" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO194" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP194" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ194" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS194" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR194" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS194" t="inlineStr"/>
       <c r="AT194" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU194" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV194" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA194" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB194" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC194" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -33945,7 +33933,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -33997,98 +33985,18 @@
       <c r="P195" t="n">
         <v>1</v>
       </c>
-      <c r="U195" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX</t>
-        </is>
-      </c>
-      <c r="V195" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX</t>
-        </is>
-      </c>
-      <c r="W195" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X195" t="inlineStr">
-        <is>
-          <t>Mpox</t>
-        </is>
-      </c>
-      <c r="Y195" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z195" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R195" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB195" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC195" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD195" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE195" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF195" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG195" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH195" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI195" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ195" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK195" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM195" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN195" t="b">
-        <v>1</v>
       </c>
       <c r="AO195" t="inlineStr">
         <is>
@@ -34182,17 +34090,17 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -34217,90 +34125,182 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N196" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="O196" t="n">
-        <v>20</v>
-      </c>
-      <c r="R196" t="n">
-        <v>0.07345623639039579</v>
-      </c>
-      <c r="S196" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P196" t="n">
+        <v>1</v>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X196" t="inlineStr">
+        <is>
+          <t>Mpox</t>
+        </is>
+      </c>
+      <c r="Y196" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB196" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD196" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE196" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF196" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG196" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH196" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI196" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ196" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK196" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM196" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN196" t="b">
+        <v>1</v>
       </c>
       <c r="AO196" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR196" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS196" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ196" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS196" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
+        </is>
+      </c>
       <c r="AT196" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV196" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA196" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB196" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC196" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -34332,12 +34332,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -34371,13 +34371,13 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="O197" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="R197" t="n">
-        <v>0</v>
+        <v>0.08080186002943539</v>
       </c>
       <c r="S197" t="inlineStr">
         <is>
@@ -34410,42 +34410,42 @@
       </c>
       <c r="AV197" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA197" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB197" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC197" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -34477,12 +34477,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -34529,82 +34529,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U198" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA198" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO198" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ198" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS198" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR198" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS198" t="inlineStr"/>
       <c r="AT198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV198" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA198" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB198" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC198" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -34631,7 +34617,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -34680,98 +34666,23 @@
       <c r="O199" t="n">
         <v>0</v>
       </c>
+      <c r="R199" t="n">
+        <v>0</v>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U199" t="inlineStr">
         <is>
           <t>SER_NO_FHI_714_MONTHLY</t>
         </is>
       </c>
-      <c r="V199" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W199" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X199" t="inlineStr">
-        <is>
-          <t>M-kopper</t>
-        </is>
-      </c>
-      <c r="Y199" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z199" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA199" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB199" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC199" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD199" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE199" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF199" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG199" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH199" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI199" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ199" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK199" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM199" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN199" t="b">
-        <v>1</v>
       </c>
       <c r="AO199" t="inlineStr">
         <is>
@@ -34865,17 +34776,17 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -34909,81 +34820,170 @@
         </is>
       </c>
       <c r="N200" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O200" t="n">
-        <v>10</v>
-      </c>
-      <c r="R200" t="n">
-        <v>0.002865038132769385</v>
-      </c>
-      <c r="S200" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_714_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_714_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X200" t="inlineStr">
+        <is>
+          <t>M-kopper</t>
+        </is>
+      </c>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB200" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD200" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE200" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF200" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG200" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH200" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI200" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ200" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK200" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM200" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN200" t="b">
+        <v>1</v>
       </c>
       <c r="AO200" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR200" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS200" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ200" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS200" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_714_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA200" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB200" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC200" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -35015,12 +35015,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -35045,7 +35045,7 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
@@ -35054,13 +35054,13 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O201" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R201" t="n">
-        <v>0.005717658852960364</v>
+        <v>0.002865038132769385</v>
       </c>
       <c r="S201" t="inlineStr">
         <is>
@@ -35093,42 +35093,42 @@
       </c>
       <c r="AV201" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA201" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB201" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC201" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -35160,12 +35160,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -35199,93 +35199,81 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O202" t="n">
-        <v>1</v>
-      </c>
-      <c r="P202" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R202" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.005717658852960364</v>
       </c>
       <c r="S202" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA202" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO202" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ202" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS202" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR202" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS202" t="inlineStr"/>
       <c r="AT202" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV202" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA202" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB202" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC202" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35312,7 +35300,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -35364,98 +35352,18 @@
       <c r="P203" t="n">
         <v>1</v>
       </c>
-      <c r="U203" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX</t>
-        </is>
-      </c>
-      <c r="V203" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX</t>
-        </is>
-      </c>
-      <c r="W203" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X203" t="inlineStr">
-        <is>
-          <t>Mpox</t>
-        </is>
-      </c>
-      <c r="Y203" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z203" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R203" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB203" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC203" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD203" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE203" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF203" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG203" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH203" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI203" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ203" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK203" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM203" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN203" t="b">
-        <v>1</v>
       </c>
       <c r="AO203" t="inlineStr">
         <is>
@@ -35549,17 +35457,17 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -35584,7 +35492,7 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
@@ -35593,81 +35501,173 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="O204" t="n">
-        <v>13</v>
-      </c>
-      <c r="R204" t="n">
-        <v>0.003724549572600201</v>
-      </c>
-      <c r="S204" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P204" t="n">
+        <v>1</v>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X204" t="inlineStr">
+        <is>
+          <t>Mpox</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB204" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD204" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE204" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF204" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG204" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH204" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI204" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ204" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK204" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM204" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN204" t="b">
+        <v>1</v>
       </c>
       <c r="AO204" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR204" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS204" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ204" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS204" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
+        </is>
+      </c>
       <c r="AT204" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB204" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC204" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -35699,12 +35699,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -35729,7 +35729,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
@@ -35738,13 +35738,13 @@
         </is>
       </c>
       <c r="N205" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="O205" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="R205" t="n">
-        <v>0.004900850445394598</v>
+        <v>0.003724549572600201</v>
       </c>
       <c r="S205" t="inlineStr">
         <is>
@@ -35777,42 +35777,42 @@
       </c>
       <c r="AV205" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA205" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB205" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC205" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -35844,12 +35844,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -35883,93 +35883,81 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O206" t="n">
-        <v>3</v>
-      </c>
-      <c r="P206" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R206" t="n">
-        <v>0.05079797265291142</v>
+        <v>0.004900850445394598</v>
       </c>
       <c r="S206" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA206" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO206" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ206" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS206" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR206" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS206" t="inlineStr"/>
       <c r="AT206" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35996,7 +35984,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -36048,98 +36036,18 @@
       <c r="P207" t="n">
         <v>3</v>
       </c>
-      <c r="U207" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX</t>
-        </is>
-      </c>
-      <c r="V207" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX</t>
-        </is>
-      </c>
-      <c r="W207" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X207" t="inlineStr">
-        <is>
-          <t>Mpox</t>
-        </is>
-      </c>
-      <c r="Y207" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z207" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R207" t="n">
+        <v>0.05079797265291142</v>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB207" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC207" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD207" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE207" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF207" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG207" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH207" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI207" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ207" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK207" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM207" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN207" t="b">
-        <v>1</v>
       </c>
       <c r="AO207" t="inlineStr">
         <is>
@@ -36233,17 +36141,17 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -36268,7 +36176,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
@@ -36277,81 +36185,173 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O208" t="n">
-        <v>7</v>
-      </c>
-      <c r="R208" t="n">
-        <v>0.00200552669293857</v>
-      </c>
-      <c r="S208" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="P208" t="n">
+        <v>3</v>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="W208" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X208" t="inlineStr">
+        <is>
+          <t>Mpox</t>
+        </is>
+      </c>
+      <c r="Y208" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB208" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC208" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD208" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE208" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF208" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG208" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH208" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI208" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ208" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK208" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM208" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN208" t="b">
+        <v>1</v>
       </c>
       <c r="AO208" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR208" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS208" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ208" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS208" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
+        </is>
+      </c>
       <c r="AT208" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA208" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -36383,12 +36383,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -36413,7 +36413,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
@@ -36422,13 +36422,13 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O209" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R209" t="n">
-        <v>0.003267233630263065</v>
+        <v>0.00200552669293857</v>
       </c>
       <c r="S209" t="inlineStr">
         <is>
@@ -36461,42 +36461,42 @@
       </c>
       <c r="AV209" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA209" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -36528,12 +36528,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -36567,93 +36567,81 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O210" t="n">
-        <v>1</v>
-      </c>
-      <c r="P210" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R210" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.003267233630263065</v>
       </c>
       <c r="S210" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA210" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO210" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ210" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS210" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR210" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS210" t="inlineStr"/>
       <c r="AT210" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV210" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA210" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB210" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC210" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36680,7 +36668,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -36732,98 +36720,18 @@
       <c r="P211" t="n">
         <v>1</v>
       </c>
-      <c r="U211" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX</t>
-        </is>
-      </c>
-      <c r="V211" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX</t>
-        </is>
-      </c>
-      <c r="W211" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X211" t="inlineStr">
-        <is>
-          <t>Mpox</t>
-        </is>
-      </c>
-      <c r="Y211" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z211" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R211" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB211" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC211" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD211" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE211" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF211" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG211" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH211" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI211" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ211" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK211" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM211" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN211" t="b">
-        <v>1</v>
       </c>
       <c r="AO211" t="inlineStr">
         <is>
@@ -36917,123 +36825,360 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>猴痘</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N212" t="n">
+        <v>1</v>
+      </c>
+      <c r="O212" t="n">
+        <v>1</v>
+      </c>
+      <c r="P212" t="n">
+        <v>1</v>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X212" t="inlineStr">
+        <is>
+          <t>Mpox</t>
+        </is>
+      </c>
+      <c r="Y212" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB212" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD212" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE212" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF212" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG212" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH212" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI212" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ212" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK212" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM212" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN212" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO212" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP212" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ212" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS212" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
+        </is>
+      </c>
+      <c r="AT212" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU212" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV212" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW212" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX212" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY212" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA212" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB212" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC212" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>monkeypox</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F212" t="inlineStr">
+      <c r="F213" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G212" t="inlineStr">
+      <c r="G213" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>D065</t>
-        </is>
-      </c>
-      <c r="I212" t="inlineStr">
-        <is>
-          <t>Monkeypox</t>
-        </is>
-      </c>
-      <c r="J212" t="inlineStr">
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
         <is>
           <t>猴痘</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr">
+      <c r="K213" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L212" t="inlineStr">
+      <c r="L213" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="M212" t="inlineStr">
+      <c r="M213" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N212" t="n">
+      <c r="N213" t="n">
         <v>10</v>
       </c>
-      <c r="O212" t="n">
+      <c r="O213" t="n">
         <v>10</v>
       </c>
-      <c r="R212" t="n">
+      <c r="R213" t="n">
         <v>0.002865038132769385</v>
       </c>
-      <c r="S212" t="inlineStr">
+      <c r="S213" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO212" t="inlineStr">
+      <c r="AO213" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP212" t="inlineStr">
+      <c r="AP213" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR212" t="inlineStr">
+      <c r="AR213" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS212" t="inlineStr"/>
-      <c r="AT212" t="n">
+      <c r="AS213" t="inlineStr"/>
+      <c r="AT213" t="n">
         <v>0</v>
       </c>
-      <c r="AU212" t="inlineStr">
+      <c r="AU213" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV212" t="inlineStr">
+      <c r="AV213" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW212" t="inlineStr">
+      <c r="AW213" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX212" t="inlineStr">
+      <c r="AX213" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY212" t="inlineStr">
+      <c r="AY213" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ212" t="inlineStr">
+      <c r="AZ213" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA212" t="inlineStr">
+      <c r="BA213" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB212" t="inlineStr">
+      <c r="BB213" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC212" t="inlineStr">
+      <c r="BC213" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -37155,7 +37300,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10">
@@ -37165,7 +37310,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -37217,7 +37362,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1052</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d065/2026-2029.xlsx
+++ b/diseases/d065/2026-2029.xlsx
@@ -34371,13 +34371,13 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="O197" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="R197" t="n">
-        <v>0.08080186002943539</v>
+        <v>0.09916591912703433</v>
       </c>
       <c r="S197" t="inlineStr">
         <is>
@@ -37362,7 +37362,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1055</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d065/2026-2029.xlsx
+++ b/diseases/d065/2026-2029.xlsx
@@ -35933,13 +35933,13 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O208" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="R208" t="n">
-        <v>0.157930908239351</v>
+        <v>0.1616037200588708</v>
       </c>
       <c r="S208" t="inlineStr">
         <is>
@@ -40349,13 +40349,13 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R235" t="n">
-        <v>0</v>
+        <v>0.00367281181951979</v>
       </c>
       <c r="S235" t="inlineStr">
         <is>
@@ -41143,7 +41143,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1132</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="16">
